--- a/Employee_Reports_wi48/Ruben Dela Cruz Malabo Q0275.xlsx
+++ b/Employee_Reports_wi48/Ruben Dela Cruz Malabo Q0275.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -912,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1010,11 +1010,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1059,11 +1059,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1108,11 +1108,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1206,11 +1206,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1255,11 +1255,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1304,11 +1304,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1353,11 +1353,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1402,11 +1402,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1451,11 +1451,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1500,11 +1500,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1549,11 +1549,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1598,11 +1598,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1647,11 +1647,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1696,11 +1696,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1745,11 +1745,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1794,11 +1794,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1817,9 +1817,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
           <t>11-Jun-2026</t>
@@ -1831,11 +1843,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1880,11 +1892,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1929,11 +1941,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1966,11 +1978,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
